--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1048,6 +1048,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1057,7 +1060,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1389,6 +1392,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1432,7 +1438,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1765,6 +1771,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1774,7 +1783,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2103,6 +2112,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2146,7 +2158,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2479,6 +2491,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2488,7 +2503,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2820,6 +2835,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2842,11 +2860,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99720192"/>
-        <c:axId val="103724160"/>
+        <c:axId val="466969344"/>
+        <c:axId val="466970880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99720192"/>
+        <c:axId val="466969344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2889,14 +2907,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103724160"/>
+        <c:crossAx val="466970880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103724160"/>
+        <c:axId val="466970880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2945,7 +2963,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99720192"/>
+        <c:crossAx val="466969344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3142,7 +3160,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3439,6 +3457,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3448,7 +3469,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3745,6 +3766,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>1179.7195080910908</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1212.9135345867317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3787,7 +3811,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4084,6 +4108,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4093,7 +4120,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4390,6 +4417,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>1725.915575606366</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1759.0798296952728</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4432,7 +4462,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4729,6 +4759,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4738,7 +4771,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5035,6 +5068,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>546.16629510854114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5056,11 +5092,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399840384"/>
-        <c:axId val="399842304"/>
+        <c:axId val="479904512"/>
+        <c:axId val="479906048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399840384"/>
+        <c:axId val="479904512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5103,14 +5139,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399842304"/>
+        <c:crossAx val="479906048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399842304"/>
+        <c:axId val="479906048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5159,7 +5195,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399840384"/>
+        <c:crossAx val="479904512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5356,7 +5392,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5653,6 +5689,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5662,7 +5701,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5959,6 +5998,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>250.30355595263484</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>255.16118173985649</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6001,7 +6043,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6298,6 +6340,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6307,7 +6352,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6604,6 +6649,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>380.48679167107468</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>385.34388479183116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6646,7 +6694,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6943,6 +6991,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6952,7 +7003,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7249,6 +7300,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>130.18270305197467</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7270,11 +7324,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442374784"/>
-        <c:axId val="448737664"/>
+        <c:axId val="479938432"/>
+        <c:axId val="479939968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442374784"/>
+        <c:axId val="479938432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7317,14 +7371,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448737664"/>
+        <c:crossAx val="479939968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448737664"/>
+        <c:axId val="479939968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7373,7 +7427,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442374784"/>
+        <c:crossAx val="479938432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7481,7 +7535,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7524,7 +7578,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7567,7 +7621,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7880,7 +7934,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF114"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12564,6 +12618,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="115" spans="1:11" ht="12.75">
+      <c r="A115" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B115" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.1747980992467859</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I115" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J115" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K115" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12580,7 +12669,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF102"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16722,6 +16811,41 @@
         <v>1725.4194238613065</v>
       </c>
     </row>
+    <row r="103" spans="1:11" ht="12.75">
+      <c r="A103" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B103" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C103" s="20">
+        <v>1.8694703600000002</v>
+      </c>
+      <c r="D103" s="21">
+        <v>33.194026495640955</v>
+      </c>
+      <c r="E103" s="22">
+        <v>19.263796983188126</v>
+      </c>
+      <c r="F103" s="22">
+        <v>19.53445522622572</v>
+      </c>
+      <c r="G103" s="22">
+        <v>33.66040583396633</v>
+      </c>
+      <c r="H103" s="22">
+        <v>1212.9135345867317</v>
+      </c>
+      <c r="I103" s="22">
+        <v>1759.0798296952728</v>
+      </c>
+      <c r="J103" s="22">
+        <v>546.16629510854114</v>
+      </c>
+      <c r="K103" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -16738,7 +16862,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AF102"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20880,6 +21004,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="103" spans="1:11" ht="12.75">
+      <c r="A103" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B103" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C103" s="20">
+        <v>1.8694703600000002</v>
+      </c>
+      <c r="D103" s="21">
+        <v>4.8576257872216422</v>
+      </c>
+      <c r="E103" s="22">
+        <v>2.8190709854866678</v>
+      </c>
+      <c r="F103" s="22">
+        <v>2.8239134078971615</v>
+      </c>
+      <c r="G103" s="22">
+        <v>4.8659699105498362</v>
+      </c>
+      <c r="H103" s="22">
+        <v>255.16118173985649</v>
+      </c>
+      <c r="I103" s="22">
+        <v>385.34388479183116</v>
+      </c>
+      <c r="J103" s="22">
+        <v>130.18270305197467</v>
+      </c>
+      <c r="K103" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1051,6 +1051,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1060,7 +1063,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1395,6 +1398,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1438,7 +1444,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1774,6 +1780,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1783,7 +1792,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2115,6 +2124,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2158,7 +2170,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2494,6 +2506,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2503,7 +2518,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2838,6 +2853,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2860,11 +2878,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="466969344"/>
-        <c:axId val="466970880"/>
+        <c:axId val="521881088"/>
+        <c:axId val="541883008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="466969344"/>
+        <c:axId val="521881088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2907,14 +2925,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466970880"/>
+        <c:crossAx val="541883008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466970880"/>
+        <c:axId val="541883008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2963,7 +2981,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466969344"/>
+        <c:crossAx val="521881088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3160,7 +3178,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3460,6 +3478,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3469,7 +3490,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3769,6 +3790,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>1212.9135345867317</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1296.0589602077778</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3811,7 +3835,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4111,6 +4135,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4120,7 +4147,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4420,6 +4447,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>1759.0798296952728</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1840.562677832015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4462,7 +4492,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4762,6 +4792,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4771,7 +4804,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5071,6 +5104,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>546.16629510854114</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>544.5037176242372</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5092,11 +5128,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479904512"/>
-        <c:axId val="479906048"/>
+        <c:axId val="570527744"/>
+        <c:axId val="570529280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479904512"/>
+        <c:axId val="570527744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5139,14 +5175,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479906048"/>
+        <c:crossAx val="570529280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479906048"/>
+        <c:axId val="570529280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5195,7 +5231,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479904512"/>
+        <c:crossAx val="570527744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5392,7 +5428,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5692,6 +5728,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5701,7 +5740,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6001,6 +6040,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>255.16118173985649</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>274.41831749964462</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6043,7 +6085,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6343,6 +6385,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6352,7 +6397,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6652,6 +6697,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>385.34388479183116</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>404.36067728147316</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6694,7 +6742,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6994,6 +7042,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7003,7 +7054,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7303,6 +7354,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>130.18270305197467</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>129.94235978182854</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7324,11 +7378,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479938432"/>
-        <c:axId val="479939968"/>
+        <c:axId val="678419840"/>
+        <c:axId val="97739904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479938432"/>
+        <c:axId val="678419840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7371,14 +7425,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479939968"/>
+        <c:crossAx val="97739904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479939968"/>
+        <c:axId val="97739904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7427,7 +7481,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479938432"/>
+        <c:crossAx val="678419840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7535,7 +7589,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7578,7 +7632,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7621,7 +7675,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7934,7 +7988,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF115"/>
+  <dimension ref="A1:AF116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12653,6 +12707,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="116" spans="1:11" ht="12.75">
+      <c r="A116" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B116" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.1794961447368402</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I116" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J116" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K116" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12669,7 +12758,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF103"/>
+  <dimension ref="A1:AF104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16846,6 +16935,41 @@
         <v>1725.4194238613065</v>
       </c>
     </row>
+    <row r="104" spans="1:11" ht="12.75">
+      <c r="A104" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B104" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C104" s="20">
+        <v>1.8696278799999997</v>
+      </c>
+      <c r="D104" s="21">
+        <v>83.145425621046073</v>
+      </c>
+      <c r="E104" s="22">
+        <v>50.759713325262247</v>
+      </c>
+      <c r="F104" s="22">
+        <v>70.294168551487971</v>
+      </c>
+      <c r="G104" s="22">
+        <v>115.14325397070833</v>
+      </c>
+      <c r="H104" s="22">
+        <v>1296.0589602077778</v>
+      </c>
+      <c r="I104" s="22">
+        <v>1840.562677832015</v>
+      </c>
+      <c r="J104" s="22">
+        <v>544.5037176242372</v>
+      </c>
+      <c r="K104" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -16862,7 +16986,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AF103"/>
+  <dimension ref="A1:AF104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21039,6 +21163,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="104" spans="1:11" ht="12.75">
+      <c r="A104" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B104" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C104" s="20">
+        <v>1.8696278799999997</v>
+      </c>
+      <c r="D104" s="21">
+        <v>19.257135759788135</v>
+      </c>
+      <c r="E104" s="22">
+        <v>11.756349592671722</v>
+      </c>
+      <c r="F104" s="22">
+        <v>14.580263000568884</v>
+      </c>
+      <c r="G104" s="22">
+        <v>23.882762400191844</v>
+      </c>
+      <c r="H104" s="22">
+        <v>274.41831749964462</v>
+      </c>
+      <c r="I104" s="22">
+        <v>404.36067728147316</v>
+      </c>
+      <c r="J104" s="22">
+        <v>129.94235978182854</v>
+      </c>
+      <c r="K104" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1054,6 +1054,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1063,7 +1066,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1401,6 +1404,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1444,7 +1450,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1783,6 +1789,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1792,7 +1801,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2127,6 +2136,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2170,7 +2182,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2509,6 +2521,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2518,7 +2533,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2856,6 +2871,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2878,11 +2896,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="521881088"/>
-        <c:axId val="541883008"/>
+        <c:axId val="387867392"/>
+        <c:axId val="387868928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="521881088"/>
+        <c:axId val="387867392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2925,14 +2943,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541883008"/>
+        <c:crossAx val="387868928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="541883008"/>
+        <c:axId val="387868928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2981,7 +2999,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521881088"/>
+        <c:crossAx val="387867392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3178,7 +3196,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3481,6 +3499,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3490,7 +3511,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3793,6 +3814,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>1296.0589602077778</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1313.9812666064583</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3835,7 +3859,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4138,6 +4162,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4147,7 +4174,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4450,6 +4477,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>1840.562677832015</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1866.9343432905844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4492,7 +4522,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4795,6 +4825,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4804,7 +4837,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5107,6 +5140,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>544.5037176242372</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>552.95307668412602</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5128,11 +5164,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="570527744"/>
-        <c:axId val="570529280"/>
+        <c:axId val="419298688"/>
+        <c:axId val="428227200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="570527744"/>
+        <c:axId val="419298688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5175,14 +5211,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="570529280"/>
+        <c:crossAx val="428227200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="570529280"/>
+        <c:axId val="428227200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5231,7 +5267,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="570527744"/>
+        <c:crossAx val="419298688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5428,7 +5464,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5731,6 +5767,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5740,7 +5779,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6043,6 +6082,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>274.41831749964462</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>276.34550955872504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6085,7 +6127,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6388,6 +6430,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6397,7 +6442,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6700,6 +6745,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>404.36067728147316</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>408.04041695322195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6742,7 +6790,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -7045,6 +7093,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7054,7 +7105,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7357,6 +7408,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>129.94235978182854</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>131.69490739449691</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7378,11 +7432,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="678419840"/>
-        <c:axId val="97739904"/>
+        <c:axId val="485507456"/>
+        <c:axId val="485508992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="678419840"/>
+        <c:axId val="485507456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7425,14 +7479,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97739904"/>
+        <c:crossAx val="485508992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="97739904"/>
+        <c:axId val="485508992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7481,7 +7535,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="678419840"/>
+        <c:crossAx val="485507456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7589,7 +7643,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7632,7 +7686,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7675,7 +7729,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7988,7 +8042,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF116"/>
+  <dimension ref="A1:AF117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12742,6 +12796,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="117" spans="1:11" ht="12.75">
+      <c r="A117" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B117" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C117" s="20">
+        <v>1.1845099478487591</v>
+      </c>
+      <c r="D117" s="21">
+        <v>0</v>
+      </c>
+      <c r="E117" s="22">
+        <v>0</v>
+      </c>
+      <c r="F117" s="22">
+        <v>0</v>
+      </c>
+      <c r="G117" s="22">
+        <v>0</v>
+      </c>
+      <c r="H117" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I117" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J117" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K117" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12758,7 +12847,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF104"/>
+  <dimension ref="A1:AF105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16970,6 +17059,41 @@
         <v>1725.4194238613065</v>
       </c>
     </row>
+    <row r="105" spans="1:11" ht="12.75">
+      <c r="A105" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B105" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C105" s="20">
+        <v>1.8657503599999992</v>
+      </c>
+      <c r="D105" s="21">
+        <v>17.922306398680565</v>
+      </c>
+      <c r="E105" s="22">
+        <v>10.193437908043682</v>
+      </c>
+      <c r="F105" s="22">
+        <v>80.487606459531648</v>
+      </c>
+      <c r="G105" s="22">
+        <v>141.51491942927774</v>
+      </c>
+      <c r="H105" s="22">
+        <v>1313.9812666064583</v>
+      </c>
+      <c r="I105" s="22">
+        <v>1866.9343432905844</v>
+      </c>
+      <c r="J105" s="22">
+        <v>552.95307668412602</v>
+      </c>
+      <c r="K105" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -16986,7 +17110,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AF104"/>
+  <dimension ref="A1:AF105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21198,6 +21322,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="105" spans="1:11" ht="12.75">
+      <c r="A105" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B105" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C105" s="20">
+        <v>1.8657503599999992</v>
+      </c>
+      <c r="D105" s="21">
+        <v>1.9271920590804075</v>
+      </c>
+      <c r="E105" s="22">
+        <v>1.0961040478895743</v>
+      </c>
+      <c r="F105" s="22">
+        <v>15.676367048458458</v>
+      </c>
+      <c r="G105" s="22">
+        <v>27.562502071940632</v>
+      </c>
+      <c r="H105" s="22">
+        <v>276.34550955872504</v>
+      </c>
+      <c r="I105" s="22">
+        <v>408.04041695322195</v>
+      </c>
+      <c r="J105" s="22">
+        <v>131.69490739449691</v>
+      </c>
+      <c r="K105" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
